--- a/dashboard_template.xlsx
+++ b/dashboard_template.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_months" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经营数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="样例查看" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经营数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,10 +68,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00C0C8B8"/>
-      <sz val="8"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="008A9A8A"/>
       <sz val="9"/>
@@ -78,6 +75,15 @@
     <font>
       <color rgb="00A0B0A0"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003A5C3A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <color rgb="008A9A8A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -128,12 +134,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -147,12 +155,11 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,11 +526,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,89 +551,101 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>切换到「经营数据」sheet，将黄色单元格 B1 改成你的公司名称</t>
+          <t>切换到「经营数据」sheet，把黄色 B1 改成你的公司名称</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>② 月份</t>
+          <t>② 设定月份</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>月份列已预设2023年1月~2025年12月，自带下拉选择，无需手填</t>
+          <t>从第3行（科目行）的月份列点击下拉箭头，选择对应的年和月</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>③ 填写数字</t>
+          <t>③ 增加月份列</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>在对应科目行的月份列下填入金额（单位：元），不要加逗号或货币符号</t>
+          <t>如需更多月份 → 右键月份列 → 复制 → 插入复制的单元格</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  例：营业收入100万元 → 填 1000000</t>
+          <t>④ 填写数字</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>员工人数直接填数字，如 42</t>
+          <t>在对应科目行填入金额（单位：元），不加逗号，不加符号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>④ 空值处理</t>
+          <t xml:space="preserve">  例：营收100万 → 填 1000000</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>某月没有数据可不填，系统自动按0处理</t>
+          <t>员工人数直接填数字，如 42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>⑤ 科目名不能改</t>
+          <t>⑤ 空值不填</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>8个科目名称（营业收入、营业成本等）必须保留，系统靠名称识别</t>
+          <t>某月没数据就留空，系统自动按0处理</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>⑥ 多公司</t>
+          <t>⑥ 科目名不能改</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>有多少家公司就填多少个Excel文件，一次上传</t>
+          <t>8个科目名称保留不动，系统识别用</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>⑦ 多公司</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>每个公司一个Excel文件，可一次上传多个</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>⬇ 填写完成后，切换到「经营数据」sheet 查看数据。</t>
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>⬇ 设置好月份后，开始填写数据 ↓</t>
         </is>
       </c>
     </row>
@@ -641,258 +660,930 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2020-01</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2020-02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2020-03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2020-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2020-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2020-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2020-07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2020-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2020-09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2020-10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2020-11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2020-12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2021-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2021-02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2021-03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2021-04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2021-05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2021-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2021-07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2021-08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2021-09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2021-10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2021-11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2021-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2022-02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2022-04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2022-05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2022-06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2022-08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-09</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2022-10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2022-11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>2025-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2027-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2027-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2028-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2028-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2028-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2028-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2029-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2029-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2029-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2029-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2029-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2029-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2029-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2029-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2029-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2029-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2029-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2029-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2030-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2030-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2030-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2030-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2030-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2030-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2030-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2030-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2030-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2030-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2030-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2030-12</t>
         </is>
       </c>
     </row>
@@ -904,66 +1595,71 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00D4A84B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>📊 填写示例（仅供参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>想看真实样例 → 打开 鼎盛医疗.xlsx / 恒达器械.xlsx / 锐新科技.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="003A5C3A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>公司名称</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>在此填写公司名称</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>← 将这里改成你的公司名称</t>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>← 改成你的公司名</t>
         </is>
       </c>
     </row>
@@ -971,629 +1667,215 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>2023-02</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>2023-04</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>2023-07</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="O3" s="9" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="P3" s="9" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="Q3" s="9" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="R3" s="9" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="S3" s="9" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="T3" s="9" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="U3" s="9" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="V3" s="9" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="X3" s="9" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="Y3" s="9" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="Z3" s="9" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="AA3" s="9" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="AB3" s="9" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="AC3" s="9" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="AD3" s="9" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="AE3" s="9" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="AF3" s="9" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="AG3" s="9" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="AH3" s="9" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AI3" s="9" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="AJ3" s="9" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="AK3" s="9" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
+      <c r="B3" s="11" t="inlineStr"/>
+      <c r="C3" s="11" t="inlineStr"/>
+      <c r="D3" s="11" t="inlineStr"/>
+      <c r="E3" s="11" t="inlineStr"/>
+      <c r="F3" s="11" t="inlineStr"/>
+      <c r="G3" s="11" t="inlineStr"/>
+      <c r="H3" s="11" t="inlineStr"/>
+      <c r="I3" s="11" t="inlineStr"/>
+      <c r="J3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr"/>
+      <c r="L3" s="11" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>营业收入</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr"/>
-      <c r="C4" s="11" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr"/>
-      <c r="G4" s="11" t="inlineStr"/>
-      <c r="H4" s="11" t="inlineStr"/>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr"/>
-      <c r="K4" s="11" t="inlineStr"/>
-      <c r="L4" s="11" t="inlineStr"/>
-      <c r="M4" s="11" t="inlineStr"/>
-      <c r="N4" s="11" t="inlineStr"/>
-      <c r="O4" s="11" t="inlineStr"/>
-      <c r="P4" s="11" t="inlineStr"/>
-      <c r="Q4" s="11" t="inlineStr"/>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr"/>
-      <c r="T4" s="11" t="inlineStr"/>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr"/>
-      <c r="W4" s="11" t="inlineStr"/>
-      <c r="X4" s="11" t="inlineStr"/>
-      <c r="Y4" s="11" t="inlineStr"/>
-      <c r="Z4" s="11" t="inlineStr"/>
-      <c r="AA4" s="11" t="inlineStr"/>
-      <c r="AB4" s="11" t="inlineStr"/>
-      <c r="AC4" s="11" t="inlineStr"/>
-      <c r="AD4" s="11" t="inlineStr"/>
-      <c r="AE4" s="11" t="inlineStr"/>
-      <c r="AF4" s="11" t="inlineStr"/>
-      <c r="AG4" s="11" t="inlineStr"/>
-      <c r="AH4" s="11" t="inlineStr"/>
-      <c r="AI4" s="11" t="inlineStr"/>
-      <c r="AJ4" s="11" t="inlineStr"/>
-      <c r="AK4" s="11" t="inlineStr"/>
-      <c r="AL4" s="12" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
+      <c r="B4" s="13" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="13" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="13" t="inlineStr"/>
+      <c r="G4" s="13" t="inlineStr"/>
+      <c r="H4" s="13" t="inlineStr"/>
+      <c r="I4" s="13" t="inlineStr"/>
+      <c r="J4" s="13" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr"/>
+      <c r="M4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>营业成本</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr"/>
-      <c r="C5" s="11" t="inlineStr"/>
-      <c r="D5" s="11" t="inlineStr"/>
-      <c r="E5" s="11" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr"/>
-      <c r="H5" s="11" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
-      <c r="L5" s="11" t="inlineStr"/>
-      <c r="M5" s="11" t="inlineStr"/>
-      <c r="N5" s="11" t="inlineStr"/>
-      <c r="O5" s="11" t="inlineStr"/>
-      <c r="P5" s="11" t="inlineStr"/>
-      <c r="Q5" s="11" t="inlineStr"/>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr"/>
-      <c r="T5" s="11" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr"/>
-      <c r="W5" s="11" t="inlineStr"/>
-      <c r="X5" s="11" t="inlineStr"/>
-      <c r="Y5" s="11" t="inlineStr"/>
-      <c r="Z5" s="11" t="inlineStr"/>
-      <c r="AA5" s="11" t="inlineStr"/>
-      <c r="AB5" s="11" t="inlineStr"/>
-      <c r="AC5" s="11" t="inlineStr"/>
-      <c r="AD5" s="11" t="inlineStr"/>
-      <c r="AE5" s="11" t="inlineStr"/>
-      <c r="AF5" s="11" t="inlineStr"/>
-      <c r="AG5" s="11" t="inlineStr"/>
-      <c r="AH5" s="11" t="inlineStr"/>
-      <c r="AI5" s="11" t="inlineStr"/>
-      <c r="AJ5" s="11" t="inlineStr"/>
-      <c r="AK5" s="11" t="inlineStr"/>
-      <c r="AL5" s="12" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
+      <c r="M5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>销售费用</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr"/>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="11" t="inlineStr"/>
-      <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="11" t="inlineStr"/>
-      <c r="L6" s="11" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="11" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
-      <c r="Q6" s="11" t="inlineStr"/>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="11" t="inlineStr"/>
-      <c r="X6" s="11" t="inlineStr"/>
-      <c r="Y6" s="11" t="inlineStr"/>
-      <c r="Z6" s="11" t="inlineStr"/>
-      <c r="AA6" s="11" t="inlineStr"/>
-      <c r="AB6" s="11" t="inlineStr"/>
-      <c r="AC6" s="11" t="inlineStr"/>
-      <c r="AD6" s="11" t="inlineStr"/>
-      <c r="AE6" s="11" t="inlineStr"/>
-      <c r="AF6" s="11" t="inlineStr"/>
-      <c r="AG6" s="11" t="inlineStr"/>
-      <c r="AH6" s="11" t="inlineStr"/>
-      <c r="AI6" s="11" t="inlineStr"/>
-      <c r="AJ6" s="11" t="inlineStr"/>
-      <c r="AK6" s="11" t="inlineStr"/>
-      <c r="AL6" s="12" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>管理费用</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr"/>
-      <c r="C7" s="11" t="inlineStr"/>
-      <c r="D7" s="11" t="inlineStr"/>
-      <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr"/>
-      <c r="H7" s="11" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="11" t="inlineStr"/>
-      <c r="K7" s="11" t="inlineStr"/>
-      <c r="L7" s="11" t="inlineStr"/>
-      <c r="M7" s="11" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
-      <c r="Q7" s="11" t="inlineStr"/>
-      <c r="R7" s="11" t="inlineStr"/>
-      <c r="S7" s="11" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr"/>
-      <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="11" t="inlineStr"/>
-      <c r="X7" s="11" t="inlineStr"/>
-      <c r="Y7" s="11" t="inlineStr"/>
-      <c r="Z7" s="11" t="inlineStr"/>
-      <c r="AA7" s="11" t="inlineStr"/>
-      <c r="AB7" s="11" t="inlineStr"/>
-      <c r="AC7" s="11" t="inlineStr"/>
-      <c r="AD7" s="11" t="inlineStr"/>
-      <c r="AE7" s="11" t="inlineStr"/>
-      <c r="AF7" s="11" t="inlineStr"/>
-      <c r="AG7" s="11" t="inlineStr"/>
-      <c r="AH7" s="11" t="inlineStr"/>
-      <c r="AI7" s="11" t="inlineStr"/>
-      <c r="AJ7" s="11" t="inlineStr"/>
-      <c r="AK7" s="11" t="inlineStr"/>
-      <c r="AL7" s="12" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
+      <c r="B7" s="13" t="inlineStr"/>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>财务费用</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr"/>
-      <c r="D8" s="11" t="inlineStr"/>
-      <c r="E8" s="11" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="11" t="inlineStr"/>
-      <c r="K8" s="11" t="inlineStr"/>
-      <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="11" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
-      <c r="Q8" s="11" t="inlineStr"/>
-      <c r="R8" s="11" t="inlineStr"/>
-      <c r="S8" s="11" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="11" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
-      <c r="W8" s="11" t="inlineStr"/>
-      <c r="X8" s="11" t="inlineStr"/>
-      <c r="Y8" s="11" t="inlineStr"/>
-      <c r="Z8" s="11" t="inlineStr"/>
-      <c r="AA8" s="11" t="inlineStr"/>
-      <c r="AB8" s="11" t="inlineStr"/>
-      <c r="AC8" s="11" t="inlineStr"/>
-      <c r="AD8" s="11" t="inlineStr"/>
-      <c r="AE8" s="11" t="inlineStr"/>
-      <c r="AF8" s="11" t="inlineStr"/>
-      <c r="AG8" s="11" t="inlineStr"/>
-      <c r="AH8" s="11" t="inlineStr"/>
-      <c r="AI8" s="11" t="inlineStr"/>
-      <c r="AJ8" s="11" t="inlineStr"/>
-      <c r="AK8" s="11" t="inlineStr"/>
-      <c r="AL8" s="12" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
+      <c r="B8" s="13" t="inlineStr"/>
+      <c r="C8" s="13" t="inlineStr"/>
+      <c r="D8" s="13" t="inlineStr"/>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
+      <c r="M8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>净利润</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr"/>
-      <c r="D9" s="11" t="inlineStr"/>
-      <c r="E9" s="11" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr"/>
-      <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="11" t="inlineStr"/>
-      <c r="K9" s="11" t="inlineStr"/>
-      <c r="L9" s="11" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
-      <c r="Q9" s="11" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr"/>
-      <c r="S9" s="11" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="11" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="11" t="inlineStr"/>
-      <c r="X9" s="11" t="inlineStr"/>
-      <c r="Y9" s="11" t="inlineStr"/>
-      <c r="Z9" s="11" t="inlineStr"/>
-      <c r="AA9" s="11" t="inlineStr"/>
-      <c r="AB9" s="11" t="inlineStr"/>
-      <c r="AC9" s="11" t="inlineStr"/>
-      <c r="AD9" s="11" t="inlineStr"/>
-      <c r="AE9" s="11" t="inlineStr"/>
-      <c r="AF9" s="11" t="inlineStr"/>
-      <c r="AG9" s="11" t="inlineStr"/>
-      <c r="AH9" s="11" t="inlineStr"/>
-      <c r="AI9" s="11" t="inlineStr"/>
-      <c r="AJ9" s="11" t="inlineStr"/>
-      <c r="AK9" s="11" t="inlineStr"/>
-      <c r="AL9" s="12" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
+      <c r="B9" s="13" t="inlineStr"/>
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>薪酬总额</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr"/>
-      <c r="D10" s="11" t="inlineStr"/>
-      <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr"/>
-      <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="11" t="inlineStr"/>
-      <c r="K10" s="11" t="inlineStr"/>
-      <c r="L10" s="11" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="11" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr"/>
-      <c r="Q10" s="11" t="inlineStr"/>
-      <c r="R10" s="11" t="inlineStr"/>
-      <c r="S10" s="11" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="11" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
-      <c r="W10" s="11" t="inlineStr"/>
-      <c r="X10" s="11" t="inlineStr"/>
-      <c r="Y10" s="11" t="inlineStr"/>
-      <c r="Z10" s="11" t="inlineStr"/>
-      <c r="AA10" s="11" t="inlineStr"/>
-      <c r="AB10" s="11" t="inlineStr"/>
-      <c r="AC10" s="11" t="inlineStr"/>
-      <c r="AD10" s="11" t="inlineStr"/>
-      <c r="AE10" s="11" t="inlineStr"/>
-      <c r="AF10" s="11" t="inlineStr"/>
-      <c r="AG10" s="11" t="inlineStr"/>
-      <c r="AH10" s="11" t="inlineStr"/>
-      <c r="AI10" s="11" t="inlineStr"/>
-      <c r="AJ10" s="11" t="inlineStr"/>
-      <c r="AK10" s="11" t="inlineStr"/>
-      <c r="AL10" s="12" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
+      <c r="B10" s="13" t="inlineStr"/>
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>员工人数</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr"/>
-      <c r="C11" s="13" t="inlineStr"/>
-      <c r="D11" s="13" t="inlineStr"/>
-      <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr"/>
-      <c r="H11" s="13" t="inlineStr"/>
-      <c r="I11" s="13" t="inlineStr"/>
-      <c r="J11" s="13" t="inlineStr"/>
-      <c r="K11" s="13" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr"/>
-      <c r="M11" s="13" t="inlineStr"/>
-      <c r="N11" s="13" t="inlineStr"/>
-      <c r="O11" s="13" t="inlineStr"/>
-      <c r="P11" s="13" t="inlineStr"/>
-      <c r="Q11" s="13" t="inlineStr"/>
-      <c r="R11" s="13" t="inlineStr"/>
-      <c r="S11" s="13" t="inlineStr"/>
-      <c r="T11" s="13" t="inlineStr"/>
-      <c r="U11" s="13" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="W11" s="13" t="inlineStr"/>
-      <c r="X11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
-      <c r="Z11" s="13" t="inlineStr"/>
-      <c r="AA11" s="13" t="inlineStr"/>
-      <c r="AB11" s="13" t="inlineStr"/>
-      <c r="AC11" s="13" t="inlineStr"/>
-      <c r="AD11" s="13" t="inlineStr"/>
-      <c r="AE11" s="13" t="inlineStr"/>
-      <c r="AF11" s="13" t="inlineStr"/>
-      <c r="AG11" s="13" t="inlineStr"/>
-      <c r="AH11" s="13" t="inlineStr"/>
-      <c r="AI11" s="13" t="inlineStr"/>
-      <c r="AJ11" s="13" t="inlineStr"/>
-      <c r="AK11" s="13" t="inlineStr"/>
-      <c r="AL11" s="12" t="inlineStr">
-        <is>
-          <t>（人）</t>
-        </is>
-      </c>
+      <c r="B11" s="14" t="inlineStr"/>
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="14" t="inlineStr"/>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>💡 提示：</t>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>💡 操作提示：</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>• 公司名称 → 改 B1 黄色单元格</t>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>① 第3行月份列 → 点击小箭头选择年和月（如 2024-01）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>• 月份 → 从下拉列表选择，无需手填</t>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>② 如需更多月份 → 右键月份列（如B列）→ 复制 → 再右键C列 → 插入复制的单元格</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>• 数字 → 直接填数字，不加逗号不加符号</t>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>③ 数字直接填，不加逗号不加符号。员工人数填纯数字</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>• 空值 → 不填即可，系统自动按0处理</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>• 科目名 → 不要修改，系统靠名称识别</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>• 看不懂 → 先看「填写说明」sheet</t>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>④ 科目名不要改，空的单元格不用填</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 M3 N3 O3 P3 Q3 R3 S3 T3 U3 V3 W3 X3 Y3 Z3 AA3 AB3 AC3 AD3 AE3 AF3 AG3 AH3 AI3 AJ3 AK3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="格式错误" error="请从下拉列表中选择年月格式" promptTitle="年月选择" prompt="请从列表中选择年月" type="list">
-      <formula1>=_months!$A$1:$A$36</formula1>
+    <dataValidation sqref="B3 C3 D3 E3 F3 G3 H3 I3 J3 K3 L3 M3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="格式错误" error="请从下拉列表中选择年月（格式：2024-01）" promptTitle="选择年月" prompt="点击下拉箭头，选择对应的年和月" type="list">
+      <formula1>=_months!$A$1:$A$132</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
